--- a/data/trans_dic/P80_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P80_R-Estudios-trans_dic.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,76</t>
+          <t>2,21; 5,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,29</t>
+          <t>0,33; 1,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,78</t>
+          <t>1,3; 2,76</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,52</t>
+          <t>1,47; 3,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,15</t>
+          <t>1,3; 2,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,17</t>
+          <t>1,53; 2,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,62</t>
+          <t>0,65; 2,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,69</t>
+          <t>0,72; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,17</t>
+          <t>0,82; 1,95</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,53</t>
+          <t>1,7; 2,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,82</t>
+          <t>1,16; 1,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,02</t>
+          <t>1,51; 2,27</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>26831</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11630; 29678</t>
+          <t>12795; 31721</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2545; 9754</t>
+          <t>2727; 10684</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15262; 35258</t>
+          <t>18116; 38645</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>38733</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>39366</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>88174</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22463; 57584</t>
+          <t>32693; 68573</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22055; 47980</t>
+          <t>28205; 54346</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52775; 97995</t>
+          <t>67357; 114748</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>19192</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3619; 16916</t>
+          <t>4601; 16999</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5747; 17763</t>
+          <t>5252; 16649</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11647; 28344</t>
+          <t>11816; 28159</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>134197</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45559; 87394</t>
+          <t>59644; 105197</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35783; 66517</t>
+          <t>43247; 73964</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90937; 143438</t>
+          <t>109178; 164662</t>
         </is>
       </c>
     </row>
